--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122351363</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103021</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122351363</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -781,6 +786,231 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122553073</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 3091, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574669</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6402944</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122553046</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98224</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 3091, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574629</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6402970</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122553073</v>
+        <v>122553046</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574669</v>
+        <v>574629</v>
       </c>
       <c r="R3" t="n">
-        <v>6402944</v>
+        <v>6402970</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122553046</v>
+        <v>122553073</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574629</v>
+        <v>574669</v>
       </c>
       <c r="R4" t="n">
-        <v>6402970</v>
+        <v>6402944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>122553046</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122351363</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122553046</v>
+        <v>122553073</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574629</v>
+        <v>574669</v>
       </c>
       <c r="R3" t="n">
-        <v>6402970</v>
+        <v>6402944</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122553073</v>
+        <v>122553046</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574669</v>
+        <v>574629</v>
       </c>
       <c r="R4" t="n">
-        <v>6402944</v>
+        <v>6402970</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>122553046</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>122553073</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122553046</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>122553046</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122553073</v>
+        <v>122553046</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574669</v>
+        <v>574629</v>
       </c>
       <c r="R3" t="n">
-        <v>6402944</v>
+        <v>6402970</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122553046</v>
+        <v>122553073</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574629</v>
+        <v>574669</v>
       </c>
       <c r="R4" t="n">
-        <v>6402970</v>
+        <v>6402944</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3091-2025 artfynd.xlsx
+++ b/artfynd/A 3091-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122553046</v>
+        <v>122553073</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574629</v>
+        <v>574669</v>
       </c>
       <c r="R3" t="n">
-        <v>6402970</v>
+        <v>6402944</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122553073</v>
+        <v>122553046</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574669</v>
+        <v>574629</v>
       </c>
       <c r="R4" t="n">
-        <v>6402944</v>
+        <v>6402970</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
